--- a/plausis/plausi_POL/4datawrapper.xlsx
+++ b/plausis/plausi_POL/4datawrapper.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H100"/>
+  <dimension ref="A1:H101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,28 +473,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Andreas Hauri</t>
+          <t>Simone Brander</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>männlich</t>
+          <t>weiblich</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>GLP</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2018</v>
+        <v>2022</v>
       </c>
       <c r="E2" t="n">
-        <v>2022</v>
+        <v>2026</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2018-</t>
+          <t>2022-</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -502,31 +502,31 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2018,0,2022,4 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>2022,0,2026,4 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Michael Baumer</t>
+          <t>Karin Rykart</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>männlich</t>
+          <t>weiblich</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>FDP</t>
+          <t>GP</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>2018</v>
       </c>
       <c r="E3" t="n">
-        <v>2022</v>
+        <v>2026</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -534,18 +534,18 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2018,0,2022,4 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>2018,0,2026,8 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Filippo Leutenegger</t>
+          <t>Michael Baumer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,14 +559,14 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2014</v>
+        <v>2018</v>
       </c>
       <c r="E4" t="n">
-        <v>2022</v>
+        <v>2026</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2014-</t>
+          <t>2018-</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -574,14 +574,14 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2014,0,2022,8 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>2018,0,2026,8 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Raphael Golta</t>
+          <t>Filippo Leutenegger</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -591,14 +591,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>FDP</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>2014</v>
       </c>
       <c r="E5" t="n">
-        <v>2022</v>
+        <v>2026</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -606,18 +606,18 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2014,0,2022,8 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>2014,0,2026,12 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Richard Wolff</t>
+          <t>Raphael Golta</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -627,26 +627,26 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="E6" t="n">
-        <v>2022</v>
+        <v>2026</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2013-</t>
+          <t>2014-</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2013,0,2022,9 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>2014,0,2026,12 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
@@ -670,7 +670,7 @@
         <v>2010</v>
       </c>
       <c r="E7" t="n">
-        <v>2022</v>
+        <v>2026</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -678,18 +678,18 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2010,0,2022,12 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>2010,0,2026,16 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Daniel Leupi</t>
+          <t>Andreas Hauri</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -699,69 +699,69 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>GP</t>
+          <t>GLP</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2010</v>
+        <v>2018</v>
       </c>
       <c r="E8" t="n">
-        <v>2022</v>
+        <v>2026</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2010-</t>
+          <t>2018-</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2010,0,2022,12 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>2018,0,2026,8 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Corine Mauch</t>
+          <t>Daniel Leupi</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>weiblich</t>
+          <t>männlich</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>GP</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="E9" t="n">
-        <v>2022</v>
+        <v>2026</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2009-</t>
+          <t>2010-</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2009,0,2022,13 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>2010,0,2026,16 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Karin Rykart</t>
+          <t>Corine Mauch</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -771,69 +771,69 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>GP</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2018</v>
+        <v>2009</v>
       </c>
       <c r="E10" t="n">
-        <v>2022</v>
+        <v>2026</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2018-</t>
+          <t>2009-</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2018,0,2022,4 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>2009,0,2026,17 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Claudia Nielsen</t>
+          <t>Richard Wolff</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>weiblich</t>
+          <t>männlich</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2010</v>
+        <v>2013</v>
       </c>
       <c r="E11" t="n">
-        <v>2018</v>
+        <v>2022</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2010-2018</t>
+          <t>2013-2022</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2010,0,2018,8 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>2013,0,2022,9 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Gerold Lauber</t>
+          <t>Andres Türler</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -843,33 +843,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CVP/Die Mitte</t>
+          <t>FDP</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2006</v>
+        <v>2002</v>
       </c>
       <c r="E12" t="n">
         <v>2018</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2006-2018</t>
+          <t>2002-2018</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2006,0,2018,12 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>2002,0,2018,16 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Andres Türler</t>
+          <t>Gerold Lauber</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -879,33 +879,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>FDP</t>
+          <t>CVP/Die Mitte</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2002</v>
+        <v>2006</v>
       </c>
       <c r="E13" t="n">
         <v>2018</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2002-2018</t>
+          <t>2006-2018</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2002,0,2018,16 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>2006,0,2018,12 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ruth Genner</t>
+          <t>Claudia Nielsen</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -915,69 +915,69 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>GP</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2008</v>
+        <v>2010</v>
       </c>
       <c r="E14" t="n">
-        <v>2014</v>
+        <v>2018</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2008-2014</t>
+          <t>2010-2018</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2008,0,2014,6 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>2010,0,2018,8 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Martin Waser</t>
+          <t>Ruth Genner</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>männlich</t>
+          <t>weiblich</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>GP</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2002</v>
+        <v>2008</v>
       </c>
       <c r="E15" t="n">
         <v>2014</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2002-2014</t>
+          <t>2008-2014</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2002,0,2014,12 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>2008,0,2014,6 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Martin Vollenwyder</t>
+          <t>Martin Waser</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -987,38 +987,38 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>FDP</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>2002</v>
       </c>
       <c r="E16" t="n">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2002-2013</t>
+          <t>2002-2014</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2002,0,2013,11 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>2002,0,2014,12 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Kathrin Martelli</t>
+          <t>Martin Vollenwyder</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>weiblich</t>
+          <t>männlich</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1027,34 +1027,34 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1994</v>
+        <v>2002</v>
       </c>
       <c r="E17" t="n">
-        <v>2010</v>
+        <v>2013</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1994-2010</t>
+          <t>2002-2013</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1994,0,2010,16 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>2002,0,2013,11 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Robert Neukomm</t>
+          <t>Esther Maurer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>männlich</t>
+          <t>weiblich</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1063,29 +1063,29 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1990</v>
+        <v>1998</v>
       </c>
       <c r="E18" t="n">
         <v>2010</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1990-2010</t>
+          <t>1998-2010</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1990,0,2010,20 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1998,0,2010,12 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Esther Maurer</t>
+          <t>Kathrin Martelli</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1095,33 +1095,33 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>FDP</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1998</v>
+        <v>1994</v>
       </c>
       <c r="E19" t="n">
         <v>2010</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1998-2010</t>
+          <t>1994-2010</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1998,0,2010,12 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1994,0,2010,16 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Elmar Ledergerber</t>
+          <t>Robert Neukomm</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1135,65 +1135,65 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1998</v>
+        <v>1990</v>
       </c>
       <c r="E20" t="n">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1998-2009</t>
+          <t>1990-2010</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1998,0,2009,11 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1990,0,2010,20 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Monika Stocker</t>
+          <t>Elmar Ledergerber</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>weiblich</t>
+          <t>männlich</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>GP</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1994</v>
+        <v>1998</v>
       </c>
       <c r="E21" t="n">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1994-2008</t>
+          <t>1998-2009</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1994,0,2008,14 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1998,0,2009,11 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Monika Weber</t>
+          <t>Monika Stocker</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1203,69 +1203,69 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>parteilos</t>
+          <t>GP</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1998</v>
+        <v>1994</v>
       </c>
       <c r="E22" t="n">
-        <v>2006</v>
+        <v>2008</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1998-2006</t>
+          <t>1994-2008</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1998,0,2006,8 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1994,0,2008,14 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Willy Küng</t>
+          <t>Monika Weber</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>männlich</t>
+          <t>weiblich</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CVP/Die Mitte</t>
+          <t>parteilos</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1982</v>
+        <v>1998</v>
       </c>
       <c r="E23" t="n">
-        <v>2002</v>
+        <v>2006</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1982-2002</t>
+          <t>1998-2006</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1982,0,2002,20 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1998,0,2006,8 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Thomas Wagner</t>
+          <t>Willy Küng</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1275,33 +1275,33 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>FDP</t>
+          <t>CVP/Die Mitte</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1978</v>
+        <v>1982</v>
       </c>
       <c r="E24" t="n">
         <v>2002</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1978-2002</t>
+          <t>1982-2002</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1978,0,2002,24 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1982,0,2002,20 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Josef Estermann</t>
+          <t>Thomas Wagner</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1311,38 +1311,38 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>FDP</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1990</v>
+        <v>1978</v>
       </c>
       <c r="E25" t="n">
         <v>2002</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1990-2002</t>
+          <t>1978-2002</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1990,0,2002,12 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1978,0,2002,24 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Ursula Koch</t>
+          <t>Josef Estermann</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>weiblich</t>
+          <t>männlich</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1351,14 +1351,14 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1986</v>
+        <v>1990</v>
       </c>
       <c r="E26" t="n">
-        <v>1998</v>
+        <v>2002</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1986-1998</t>
+          <t>1990-2002</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -1366,14 +1366,14 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1986,0,1998,12 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1990,0,2002,12 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Hans Wehrli</t>
+          <t>Wolfgang Nigg</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1383,33 +1383,33 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>FDP</t>
+          <t>CVP/Die Mitte</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1992</v>
+        <v>1986</v>
       </c>
       <c r="E27" t="n">
         <v>1998</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1992-1998</t>
+          <t>1986-1998</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1992,0,1998,6 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1986,0,1998,12 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Wolfgang Nigg</t>
+          <t>Hans Wehrli</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1419,62 +1419,62 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CVP/Die Mitte</t>
+          <t>FDP</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1986</v>
+        <v>1992</v>
       </c>
       <c r="E28" t="n">
         <v>1998</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1986-1998</t>
+          <t>1992-1998</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1986,0,1998,12 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1992,0,1998,6 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Rudolf Aeschbacher</t>
+          <t>Ursula Koch</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>männlich</t>
+          <t>weiblich</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>EVP</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1978</v>
+        <v>1986</v>
       </c>
       <c r="E29" t="n">
-        <v>1994</v>
+        <v>1998</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1978-1994</t>
+          <t>1986-1998</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1978,0,1994,16 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1986,0,1998,12 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
@@ -1517,7 +1517,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Jürg Kaufmann</t>
+          <t>Rudolf Aeschbacher</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1527,33 +1527,33 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>parteilos</t>
+          <t>EVP</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1974</v>
+        <v>1978</v>
       </c>
       <c r="E31" t="n">
-        <v>1992</v>
+        <v>1994</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1974-1992</t>
+          <t>1978-1994</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1974,0,1992,18 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1978,0,1994,16 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Kurt Egloff</t>
+          <t>Jürg Kaufmann</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1563,26 +1563,26 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>BGB/SVP</t>
+          <t>parteilos</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1982</v>
+        <v>1974</v>
       </c>
       <c r="E32" t="n">
-        <v>1990</v>
+        <v>1992</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1982-1990</t>
+          <t>1974-1992</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1982,0,1990,8 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1974,0,1992,18 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Max Bryner</t>
+          <t>Kurt Egloff</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1635,18 +1635,18 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Gewerkschaftsbund</t>
+          <t>BGB/SVP</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1978</v>
+        <v>1982</v>
       </c>
       <c r="E34" t="n">
-        <v>1986</v>
+        <v>1990</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1978-1986</t>
+          <t>1982-1990</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -1654,14 +1654,14 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>1978,0,1986,8 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1982,0,1990,8 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Hugo Fahrner</t>
+          <t>Max Bryner</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1671,33 +1671,33 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>FDP</t>
+          <t>Gewerkschaftsbund</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1982</v>
+        <v>1978</v>
       </c>
       <c r="E35" t="n">
         <v>1986</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1982-1986</t>
+          <t>1978-1986</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1982,0,1986,4 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1978,0,1986,8 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Max Koller</t>
+          <t>Hugo Fahrner</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1707,33 +1707,33 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CVP/Die Mitte</t>
+          <t>FDP</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1970</v>
+        <v>1982</v>
       </c>
       <c r="E36" t="n">
-        <v>1982</v>
+        <v>1986</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1970-1982</t>
+          <t>1982-1986</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>1970,0,1982,12 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1982,0,1986,4 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Edwin Frech</t>
+          <t>Max Koller</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1743,33 +1743,33 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>CVP/Die Mitte</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1966</v>
+        <v>1970</v>
       </c>
       <c r="E37" t="n">
         <v>1982</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1966-1982</t>
+          <t>1970-1982</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1966,0,1982,16 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1970,0,1982,12 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sigmund F. T. Widmer</t>
+          <t>Edwin Frech</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1779,74 +1779,74 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>LdU</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1954</v>
+        <v>1966</v>
       </c>
       <c r="E38" t="n">
         <v>1982</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1954-1982</t>
+          <t>1966-1982</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>1954,0,1982,28 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1966,0,1982,16 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Regula Pestalozzi</t>
+          <t>Sigmund F. T. Widmer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>weiblich</t>
+          <t>männlich</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>FDP</t>
+          <t>LdU</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1974</v>
+        <v>1954</v>
       </c>
       <c r="E39" t="n">
-        <v>1978</v>
+        <v>1982</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1974-1978</t>
+          <t>1954-1982</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>1974,0,1978,4 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1954,0,1982,28 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Heinrich Burkhardt</t>
+          <t>Regula Pestalozzi</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>männlich</t>
+          <t>weiblich</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1855,29 +1855,29 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1970</v>
+        <v>1974</v>
       </c>
       <c r="E40" t="n">
         <v>1978</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1970-1978</t>
+          <t>1974-1978</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>1970,0,1978,8 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1974,0,1978,4 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Jakob Baur</t>
+          <t>Heinrich Burkhardt</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1887,33 +1887,33 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>BGB/SVP</t>
+          <t>FDP</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1958</v>
+        <v>1970</v>
       </c>
       <c r="E41" t="n">
         <v>1978</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1958-1978</t>
+          <t>1970-1978</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>1958,0,1978,20 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1970,0,1978,8 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Rudolf Albert Welter</t>
+          <t>Jakob Baur</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1923,33 +1923,33 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>BGB/SVP</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1960</v>
+        <v>1958</v>
       </c>
       <c r="E42" t="n">
-        <v>1974</v>
+        <v>1978</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1960-1974</t>
+          <t>1958-1978</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>1960,0,1974,14 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1958,0,1978,20 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Adolf Maurer</t>
+          <t>Rudolf Albert Welter</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1963,29 +1963,29 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1958</v>
+        <v>1960</v>
       </c>
       <c r="E43" t="n">
         <v>1974</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>1958-1974</t>
+          <t>1960-1974</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>1958,0,1974,16 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1960,0,1974,14 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Alois Holenstein</t>
+          <t>Adolf Maurer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1995,33 +1995,33 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CVP/Die Mitte</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1950</v>
+        <v>1958</v>
       </c>
       <c r="E44" t="n">
-        <v>1970</v>
+        <v>1974</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1950-1970</t>
+          <t>1958-1974</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>1950,0,1970,20 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1958,0,1974,16 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Albert Sieber</t>
+          <t>Alois Holenstein</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2031,33 +2031,33 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>FDP</t>
+          <t>CVP/Die Mitte</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1946</v>
+        <v>1950</v>
       </c>
       <c r="E45" t="n">
         <v>1970</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1946-1970</t>
+          <t>1950-1970</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>1946,0,1970,24 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1950,0,1970,20 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>August Wilhelm Ziegler</t>
+          <t>Albert Sieber</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2067,33 +2067,33 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>FDP</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1942</v>
+        <v>1946</v>
       </c>
       <c r="E46" t="n">
         <v>1970</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1942-1970</t>
+          <t>1946-1970</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>1942,0,1970,28 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1946,0,1970,24 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Ernst Bieri</t>
+          <t>August Wilhelm Ziegler</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2103,33 +2103,33 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>FDP</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1966</v>
+        <v>1942</v>
       </c>
       <c r="E47" t="n">
         <v>1970</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1966-1970</t>
+          <t>1942-1970</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>1966,0,1970,4 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1942,0,1970,28 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Emil Landolt</t>
+          <t>Ernst Bieri</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2143,29 +2143,29 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1942</v>
+        <v>1966</v>
       </c>
       <c r="E48" t="n">
-        <v>1966</v>
+        <v>1970</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1942-1966</t>
+          <t>1966-1970</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>1942,0,1966,24 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1966,0,1970,4 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Walter Thomann</t>
+          <t>Emil Landolt</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2175,33 +2175,33 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>FDP</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1954</v>
+        <v>1942</v>
       </c>
       <c r="E49" t="n">
         <v>1966</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1954-1966</t>
+          <t>1942-1966</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>1954,0,1966,12 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1942,0,1966,24 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Willy Spühler</t>
+          <t>Walter Thomann</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2215,29 +2215,29 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1942</v>
+        <v>1954</v>
       </c>
       <c r="E50" t="n">
-        <v>1960</v>
+        <v>1966</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1942-1960</t>
+          <t>1954-1966</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>1942,0,1960,18 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1954,0,1966,12 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Hans Sappeur</t>
+          <t>Willy Spühler</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2247,33 +2247,33 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>LdU</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1949</v>
+        <v>1942</v>
       </c>
       <c r="E51" t="n">
-        <v>1958</v>
+        <v>1960</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>1949-1958</t>
+          <t>1942-1960</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>1949,0,1958,9 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1942,0,1960,18 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Jakob Peter</t>
+          <t>Hans Sappeur</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2283,33 +2283,33 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>LdU</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1938</v>
+        <v>1949</v>
       </c>
       <c r="E52" t="n">
         <v>1958</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>1938-1958</t>
+          <t>1949-1958</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>1938,0,1958,20 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1949,0,1958,9 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Heinrich Oetiker</t>
+          <t>Jakob Peter</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2319,33 +2319,33 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>LdU</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1942</v>
+        <v>1938</v>
       </c>
       <c r="E53" t="n">
-        <v>1954</v>
+        <v>1958</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>1942-1954</t>
+          <t>1938-1958</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>1942,0,1954,12 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1938,0,1958,20 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Johann Jakob Baumann</t>
+          <t>Heinrich Oetiker</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2355,33 +2355,33 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>LdU</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1928</v>
+        <v>1942</v>
       </c>
       <c r="E54" t="n">
         <v>1954</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>1928-1954</t>
+          <t>1942-1954</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>1928,0,1954,26 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1942,0,1954,12 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Edgar Woog</t>
+          <t>Johann Jakob Baumann</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2391,33 +2391,33 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>PdA</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1946</v>
+        <v>1928</v>
       </c>
       <c r="E55" t="n">
-        <v>1949</v>
+        <v>1954</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>1946-1949</t>
+          <t>1928-1954</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>1946,0,1949,3 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1928,0,1954,26 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Adolf Lüchinger</t>
+          <t>Edgar Woog</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2427,33 +2427,33 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PdA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1944</v>
+        <v>1946</v>
       </c>
       <c r="E56" t="n">
         <v>1949</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>1944-1949</t>
+          <t>1946-1949</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>1944,0,1949,5 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1946,0,1949,3 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Anton Higi</t>
+          <t>Adolf Lüchinger</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2463,33 +2463,33 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>CVP/Die Mitte</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1938</v>
+        <v>1944</v>
       </c>
       <c r="E57" t="n">
-        <v>1946</v>
+        <v>1949</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>1938-1946</t>
+          <t>1944-1949</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>1938,0,1946,8 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1944,0,1949,5 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Erwin Stirnemann</t>
+          <t>Anton Higi</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2499,33 +2499,33 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>FDP</t>
+          <t>CVP/Die Mitte</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1934</v>
+        <v>1938</v>
       </c>
       <c r="E58" t="n">
         <v>1946</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>1934-1946</t>
+          <t>1938-1946</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>1934,0,1946,12 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1938,0,1946,8 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Ernst Nobst</t>
+          <t>Erwin Stirnemann</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2535,33 +2535,33 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>FDP</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1942</v>
+        <v>1934</v>
       </c>
       <c r="E59" t="n">
-        <v>1944</v>
+        <v>1946</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>1942-1944</t>
+          <t>1934-1946</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>1942,0,1944,2 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1934,0,1946,12 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Johann Briner</t>
+          <t>Ernst Nobst</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2575,29 +2575,29 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1928</v>
+        <v>1942</v>
       </c>
       <c r="E60" t="n">
-        <v>1942</v>
+        <v>1944</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>1928-1942</t>
+          <t>1942-1944</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>1928,0,1942,14 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1942,0,1944,2 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Jakob Anton Gschwend</t>
+          <t>Johann Briner</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2611,29 +2611,29 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1922</v>
+        <v>1928</v>
       </c>
       <c r="E61" t="n">
         <v>1942</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>1922-1942</t>
+          <t>1928-1942</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>1922,0,1942,20 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1928,0,1942,14 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Joachim Hefti</t>
+          <t>Jakob Anton Gschwend</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2643,33 +2643,33 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>FDP</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1931</v>
+        <v>1922</v>
       </c>
       <c r="E62" t="n">
         <v>1942</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>1931-1942</t>
+          <t>1922-1942</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>1931,0,1942,11 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1922,0,1942,20 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Robert Kunz</t>
+          <t>Joachim Hefti</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2679,33 +2679,33 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Demokraten</t>
+          <t>FDP</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1935</v>
+        <v>1931</v>
       </c>
       <c r="E63" t="n">
         <v>1942</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>1935-1942</t>
+          <t>1931-1942</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>1935,0,1942,7 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1931,0,1942,11 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Emil Klöti</t>
+          <t>Robert Kunz</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2715,33 +2715,33 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>Demokraten</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1907</v>
+        <v>1935</v>
       </c>
       <c r="E64" t="n">
         <v>1942</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>1907-1942</t>
+          <t>1935-1942</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>1907,0,1942,35 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1935,0,1942,7 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Niklaus Bernhard Kaufmann</t>
+          <t>Emil Klöti</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2755,29 +2755,29 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1923</v>
+        <v>1907</v>
       </c>
       <c r="E65" t="n">
-        <v>1938</v>
+        <v>1942</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>1923-1938</t>
+          <t>1907-1942</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>1923,0,1938,15 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1907,0,1942,35 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Emil Buomberger</t>
+          <t>Niklaus Bernhard Kaufmann</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2787,33 +2787,33 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>CVP/Die Mitte</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1933</v>
+        <v>1923</v>
       </c>
       <c r="E66" t="n">
         <v>1938</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>1933-1938</t>
+          <t>1923-1938</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>1933,0,1938,5 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1923,0,1938,15 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Willhelm Otto Sing</t>
+          <t>Emil Buomberger</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2823,33 +2823,33 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Demokraten</t>
+          <t>CVP/Die Mitte</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1932</v>
+        <v>1933</v>
       </c>
       <c r="E67" t="n">
-        <v>1935</v>
+        <v>1938</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>1932-1935</t>
+          <t>1933-1938</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>1932,0,1935,3 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1933,0,1938,5 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Johann Gustav Kruck</t>
+          <t>Willhelm Otto Sing</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2859,33 +2859,33 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>FDP</t>
+          <t>Demokraten</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1917</v>
+        <v>1932</v>
       </c>
       <c r="E68" t="n">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>1917-1934</t>
+          <t>1932-1935</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>1917,0,1934,17 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1932,0,1935,3 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Robert Briner</t>
+          <t>Johann Gustav Kruck</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2895,33 +2895,33 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Demokraten</t>
+          <t>FDP</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1933</v>
+        <v>1917</v>
       </c>
       <c r="E69" t="n">
-        <v>1933</v>
+        <v>1934</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>1933-1933</t>
+          <t>1917-1934</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>1933,0,1933,0 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1917,0,1934,17 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Ulrich Ribi</t>
+          <t>Robert Briner</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2931,33 +2931,33 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>EVP</t>
+          <t>Demokraten</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1920</v>
+        <v>1933</v>
       </c>
       <c r="E70" t="n">
         <v>1933</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>1920-1933</t>
+          <t>1933-1933</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>1920,0,1933,13 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1933,0,1933,0 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Hermann H. Häberlin</t>
+          <t>Ulrich Ribi</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2967,33 +2967,33 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>FDP</t>
+          <t>EVP</t>
         </is>
       </c>
       <c r="D71" t="n">
         <v>1920</v>
       </c>
       <c r="E71" t="n">
-        <v>1932</v>
+        <v>1933</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>1920-1932</t>
+          <t>1920-1933</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>1920,0,1932,12 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1920,0,1933,13 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Otto A. Hungerbühler</t>
+          <t>Hermann H. Häberlin</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3007,29 +3007,29 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1928</v>
+        <v>1920</v>
       </c>
       <c r="E72" t="n">
-        <v>1931</v>
+        <v>1932</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>1928-1931</t>
+          <t>1920-1932</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>1928,0,1931,3 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1920,0,1932,12 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Ernst Höhn</t>
+          <t>Otto A. Hungerbühler</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3039,18 +3039,18 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Demokraten</t>
+          <t>FDP</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1925</v>
+        <v>1928</v>
       </c>
       <c r="E73" t="n">
-        <v>1928</v>
+        <v>1931</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>1925-1928</t>
+          <t>1928-1931</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -3058,14 +3058,14 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>1925,0,1928,3 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1928,0,1931,3 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Hans Nägeli</t>
+          <t>Ernst Höhn</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3079,29 +3079,29 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1907</v>
+        <v>1925</v>
       </c>
       <c r="E74" t="n">
         <v>1928</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>1907-1928</t>
+          <t>1925-1928</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>1907,0,1928,21 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1925,0,1928,3 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>P. Hermann Bertschinger</t>
+          <t>Hans Nägeli</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3111,33 +3111,33 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>FDP</t>
+          <t>Demokraten</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1925</v>
+        <v>1907</v>
       </c>
       <c r="E75" t="n">
-        <v>1927</v>
+        <v>1928</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>1925-1927</t>
+          <t>1907-1928</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>1925,0,1927,2 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1907,0,1928,21 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Paul Albert Rütsche</t>
+          <t>P. Hermann Bertschinger</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3151,14 +3151,14 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1923</v>
+        <v>1925</v>
       </c>
       <c r="E76" t="n">
-        <v>1925</v>
+        <v>1927</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>1923-1925</t>
+          <t>1925-1927</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -3166,14 +3166,14 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>1923,0,1925,2 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1925,0,1927,2 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Hans Kern</t>
+          <t>Paul Albert Rütsche</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3183,33 +3183,33 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Demokraten</t>
+          <t>FDP</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1914</v>
+        <v>1923</v>
       </c>
       <c r="E77" t="n">
         <v>1925</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>1914-1925</t>
+          <t>1923-1925</t>
         </is>
       </c>
       <c r="G77" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>1914,0,1925,11 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1923,0,1925,2 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Paul B. Pflüger</t>
+          <t>Hans Kern</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3219,33 +3219,33 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>Demokraten</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1910</v>
+        <v>1914</v>
       </c>
       <c r="E78" t="n">
-        <v>1923</v>
+        <v>1925</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>1910-1923</t>
+          <t>1914-1925</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>1910,0,1923,13 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1914,0,1925,11 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Alfred Traber</t>
+          <t>Paul B. Pflüger</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3259,29 +3259,29 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1919</v>
+        <v>1910</v>
       </c>
       <c r="E79" t="n">
-        <v>1922</v>
+        <v>1923</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>1919-1922</t>
+          <t>1910-1923</t>
         </is>
       </c>
       <c r="G79" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>1919,0,1922,3 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1910,0,1923,13 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Arnold Bosshardt</t>
+          <t>Alfred Traber</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3291,33 +3291,33 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>FDP</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1912</v>
+        <v>1919</v>
       </c>
       <c r="E80" t="n">
         <v>1922</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>1912-1922</t>
+          <t>1919-1922</t>
         </is>
       </c>
       <c r="G80" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>1912,0,1922,10 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1919,0,1922,3 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Johann Adolf Streuli</t>
+          <t>Arnold Bosshardt</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3331,29 +3331,29 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1914</v>
+        <v>1912</v>
       </c>
       <c r="E81" t="n">
         <v>1922</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>1914-1922</t>
+          <t>1912-1922</t>
         </is>
       </c>
       <c r="G81" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>1914,0,1922,8 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1912,0,1922,10 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Otto Ludwig Gottfried Lang</t>
+          <t>Johann Adolf Streuli</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3363,33 +3363,33 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>FDP</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1915</v>
+        <v>1914</v>
       </c>
       <c r="E82" t="n">
-        <v>1920</v>
+        <v>1922</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>1915-1920</t>
+          <t>1914-1922</t>
         </is>
       </c>
       <c r="G82" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>1915,0,1920,5 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1914,0,1922,8 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Johann Jakob Vogelsanger</t>
+          <t>Otto Ludwig Gottfried Lang</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3403,29 +3403,29 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1892</v>
+        <v>1915</v>
       </c>
       <c r="E83" t="n">
-        <v>1919</v>
+        <v>1920</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>1892-1919</t>
+          <t>1915-1920</t>
         </is>
       </c>
       <c r="G83" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>1892,0,1919,27 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1915,0,1920,5 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Robert Billeter</t>
+          <t>Johann Jakob Vogelsanger</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3435,33 +3435,33 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>FDP</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1896</v>
+        <v>1892</v>
       </c>
       <c r="E84" t="n">
-        <v>1917</v>
+        <v>1919</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>1896-1917</t>
+          <t>1892-1919</t>
         </is>
       </c>
       <c r="G84" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>1896,0,1917,21 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1892,0,1919,27 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>H. Friedrich Erismann</t>
+          <t>Robert Billeter</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3471,33 +3471,33 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>FDP</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1901</v>
+        <v>1896</v>
       </c>
       <c r="E85" t="n">
-        <v>1915</v>
+        <v>1917</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>1901-1915</t>
+          <t>1896-1917</t>
         </is>
       </c>
       <c r="G85" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>1901,0,1915,14 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1896,0,1917,21 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Heinrich Emil Schneebeli</t>
+          <t>H. Friedrich Erismann</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3507,33 +3507,33 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>FDP</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1909</v>
+        <v>1901</v>
       </c>
       <c r="E86" t="n">
-        <v>1914</v>
+        <v>1915</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>1909-1914</t>
+          <t>1901-1915</t>
         </is>
       </c>
       <c r="G86" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>1909,0,1914,5 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1901,0,1915,14 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Joseph Benjamin Fritschi</t>
+          <t>Heinrich Emil Schneebeli</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3543,33 +3543,33 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Demokraten</t>
+          <t>FDP</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1892</v>
+        <v>1909</v>
       </c>
       <c r="E87" t="n">
         <v>1914</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>1892-1914</t>
+          <t>1909-1914</t>
         </is>
       </c>
       <c r="G87" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>1892,0,1914,22 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1909,0,1914,5 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>F. M. Heinrich Mousson</t>
+          <t>Joseph Benjamin Fritschi</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3579,33 +3579,33 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>FDP</t>
+          <t>Demokraten</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1904</v>
+        <v>1892</v>
       </c>
       <c r="E88" t="n">
-        <v>1912</v>
+        <v>1914</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>1904-1912</t>
+          <t>1892-1914</t>
         </is>
       </c>
       <c r="G88" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>1904,0,1912,8 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1892,0,1914,22 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Melchior Heinrich Wyss</t>
+          <t>F. M. Heinrich Mousson</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3615,33 +3615,33 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>FDP</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1901</v>
+        <v>1904</v>
       </c>
       <c r="E89" t="n">
-        <v>1910</v>
+        <v>1912</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>1901-1910</t>
+          <t>1904-1912</t>
         </is>
       </c>
       <c r="G89" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>1901,0,1910,9 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1904,0,1912,8 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Hans Konrad Pestalozzi</t>
+          <t>Melchior Heinrich Wyss</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3651,33 +3651,33 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>FDP</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1881</v>
+        <v>1901</v>
       </c>
       <c r="E90" t="n">
-        <v>1909</v>
+        <v>1910</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>1881-1909</t>
+          <t>1901-1910</t>
         </is>
       </c>
       <c r="G90" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>1881,0,1909,28 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1901,0,1910,9 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Elias Hasler</t>
+          <t>Hans Konrad Pestalozzi</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3687,33 +3687,33 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Demokraten</t>
+          <t>FDP</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1892</v>
+        <v>1881</v>
       </c>
       <c r="E91" t="n">
-        <v>1907</v>
+        <v>1909</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>1892-1907</t>
+          <t>1881-1909</t>
         </is>
       </c>
       <c r="G91" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>1892,0,1907,15 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1881,0,1909,28 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Robert Welti</t>
+          <t>Elias Hasler</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3723,33 +3723,33 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>FDP</t>
+          <t>Demokraten</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1900</v>
+        <v>1892</v>
       </c>
       <c r="E92" t="n">
         <v>1907</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>1900-1907</t>
+          <t>1892-1907</t>
         </is>
       </c>
       <c r="G92" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>1900,0,1907,7 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1892,0,1907,15 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Johannes Süss</t>
+          <t>Robert Welti</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3763,29 +3763,29 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1896</v>
+        <v>1900</v>
       </c>
       <c r="E93" t="n">
-        <v>1904</v>
+        <v>1907</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>1896-1904</t>
+          <t>1900-1907</t>
         </is>
       </c>
       <c r="G93" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>1896,0,1904,8 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1900,0,1907,7 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Jakob Lutz</t>
+          <t>Johannes Süss</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3795,33 +3795,33 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Demokraten</t>
+          <t>FDP</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="E94" t="n">
-        <v>1901</v>
+        <v>1904</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>1897-1901</t>
+          <t>1896-1904</t>
         </is>
       </c>
       <c r="G94" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>1897,0,1901,4 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1896,0,1904,8 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Johann Caspar Grob</t>
+          <t>Jakob Lutz</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3835,29 +3835,29 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>1892</v>
+        <v>1897</v>
       </c>
       <c r="E95" t="n">
         <v>1901</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>1892-1901</t>
+          <t>1897-1901</t>
         </is>
       </c>
       <c r="G95" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>1892,0,1901,9 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1897,0,1901,4 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Ernst Hermann Müller</t>
+          <t>Johann Caspar Grob</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3871,29 +3871,29 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>1898</v>
+        <v>1892</v>
       </c>
       <c r="E96" t="n">
         <v>1901</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>1898-1901</t>
+          <t>1892-1901</t>
         </is>
       </c>
       <c r="G96" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>1898,0,1901,3 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1892,0,1901,9 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Johann Heinrich Walcher</t>
+          <t>Ernst Hermann Müller</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3903,33 +3903,33 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>FDP</t>
+          <t>Demokraten</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>1892</v>
+        <v>1898</v>
       </c>
       <c r="E97" t="n">
-        <v>1898</v>
+        <v>1901</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>1892-1898</t>
+          <t>1898-1901</t>
         </is>
       </c>
       <c r="G97" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>1892,0,1898,6 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1898,0,1901,3 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Johannes Schneider</t>
+          <t>Johann Heinrich Walcher</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3939,33 +3939,33 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Demokraten</t>
+          <t>FDP</t>
         </is>
       </c>
       <c r="D98" t="n">
         <v>1892</v>
       </c>
       <c r="E98" t="n">
-        <v>1897</v>
+        <v>1898</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>1892-1897</t>
+          <t>1892-1898</t>
         </is>
       </c>
       <c r="G98" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>1892,0,1897,5 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1892,0,1898,6 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Paul Konrad Emil Usteri</t>
+          <t>Johannes Schneider</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3975,33 +3975,33 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>FDP</t>
+          <t>Demokraten</t>
         </is>
       </c>
       <c r="D99" t="n">
         <v>1892</v>
       </c>
       <c r="E99" t="n">
-        <v>1896</v>
+        <v>1897</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>1892-1896</t>
+          <t>1892-1897</t>
         </is>
       </c>
       <c r="G99" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>1892,0,1896,4 @width:0.9 @color:grey @opacity:0.3</t>
+          <t>1892,0,1897,5 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Johann August Koller</t>
+          <t>Paul Konrad Emil Usteri</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4011,24 +4011,60 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Demokraten</t>
+          <t>FDP</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>1885</v>
+        <v>1892</v>
       </c>
       <c r="E100" t="n">
         <v>1896</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
+          <t>1892-1896</t>
+        </is>
+      </c>
+      <c r="G100" t="n">
+        <v>4</v>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>1892,0,1896,4 @width:0.9 @color:grey @opacity:0.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Johann August Koller</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>männlich</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Demokraten</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>1885</v>
+      </c>
+      <c r="E101" t="n">
+        <v>1896</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
           <t>1885-1896</t>
         </is>
       </c>
-      <c r="G100" t="n">
+      <c r="G101" t="n">
         <v>11</v>
       </c>
-      <c r="H100" t="inlineStr">
+      <c r="H101" t="inlineStr">
         <is>
           <t>1885,0,1896,11 @width:0.9 @color:grey @opacity:0.3</t>
         </is>
